--- a/AAII_Financials/Quarterly/AGRO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AGRO_QTR_FIN.xlsx
@@ -2034,7 +2034,7 @@
         <v>5700</v>
       </c>
       <c r="G20" s="3">
-        <v>-33000</v>
+        <v>-30400</v>
       </c>
       <c r="H20" s="3">
         <v>39900</v>
@@ -2153,7 +2153,7 @@
         <v>49800</v>
       </c>
       <c r="G21" s="3">
-        <v>44800</v>
+        <v>42200</v>
       </c>
       <c r="H21" s="3">
         <v>60000</v>
@@ -2269,10 +2269,10 @@
         <v>31500</v>
       </c>
       <c r="F22" s="3">
-        <v>15700</v>
+        <v>22700</v>
       </c>
       <c r="G22" s="3">
-        <v>21500</v>
+        <v>18900</v>
       </c>
       <c r="H22" s="3">
         <v>15900</v>
@@ -3462,7 +3462,7 @@
         <v>-5700</v>
       </c>
       <c r="G32" s="3">
-        <v>33000</v>
+        <v>30400</v>
       </c>
       <c r="H32" s="3">
         <v>-39900</v>
@@ -6132,10 +6132,10 @@
         <v>78300</v>
       </c>
       <c r="E59" s="3">
-        <v>45800</v>
+        <v>35700</v>
       </c>
       <c r="F59" s="3">
-        <v>44100</v>
+        <v>34800</v>
       </c>
       <c r="G59" s="3">
         <v>45500</v>
